--- a/contenus/tab2/exs4-sierreur-recherchev.xlsx
+++ b/contenus/tab2/exs4-sierreur-recherchev.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consignes" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exercice" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correction" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -888,255 +887,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Référence</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Quantité commandée</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Prix unitaire (€)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>REF301</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C2">
-        <f>IFERROR(VLOOKUP(A2,$F$2:$G$11,2,FALSE),"Référence inconnue")</f>
-        <v/>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>REF301</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REF399</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>14</v>
-      </c>
-      <c r="C3">
-        <f>IFERROR(VLOOKUP(A3,$F$2:$G$11,2,FALSE),"Référence inconnue")</f>
-        <v/>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>REF302</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>25.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REF303</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>17</v>
-      </c>
-      <c r="C4">
-        <f>IFERROR(VLOOKUP(A4,$F$2:$G$11,2,FALSE),"Référence inconnue")</f>
-        <v/>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>REF303</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REF304</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>20</v>
-      </c>
-      <c r="C5">
-        <f>IFERROR(VLOOKUP(A5,$F$2:$G$11,2,FALSE),"Référence inconnue")</f>
-        <v/>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>REF304</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REF320</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>23</v>
-      </c>
-      <c r="C6">
-        <f>IFERROR(VLOOKUP(A6,$F$2:$G$11,2,FALSE),"Référence inconnue")</f>
-        <v/>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>REF305</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>15.2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REF306</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <f>IFERROR(VLOOKUP(A7,$F$2:$G$11,2,FALSE),"Référence inconnue")</f>
-        <v/>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>REF306</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REF307</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>9</v>
-      </c>
-      <c r="C8">
-        <f>IFERROR(VLOOKUP(A8,$F$2:$G$11,2,FALSE),"Référence inconnue")</f>
-        <v/>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>REF307</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REF308</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>12</v>
-      </c>
-      <c r="C9">
-        <f>IFERROR(VLOOKUP(A9,$F$2:$G$11,2,FALSE),"Référence inconnue")</f>
-        <v/>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>REF308</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REF350</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <f>IFERROR(VLOOKUP(A10,$F$2:$G$11,2,FALSE),"Référence inconnue")</f>
-        <v/>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>REF309</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>12.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>REF310</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>18</v>
-      </c>
-      <c r="C11">
-        <f>IFERROR(VLOOKUP(A11,$F$2:$G$11,2,FALSE),"Référence inconnue")</f>
-        <v/>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>REF310</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>